--- a/Rekap Kas Rumdin (1).xlsx
+++ b/Rekap Kas Rumdin (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muhammad.syafrizal02\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6320FD-0630-471E-8040-47DF54EF858C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102C5610-EC41-418A-97E1-EAB35ADC6FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="50">
   <si>
     <t>Tanggal</t>
   </si>
@@ -114,12 +114,6 @@
     <t>Bayar Laundry</t>
   </si>
   <si>
-    <t>Split Pemeliharaan Rumput</t>
-  </si>
-  <si>
-    <t>Split Obat Rumput</t>
-  </si>
-  <si>
     <t>Sewa Rumdin</t>
   </si>
   <si>
@@ -163,16 +157,44 @@
   </si>
   <si>
     <t>Kunci Jendela, Kelengkapan Cat (Roller, amplas, dll)</t>
+  </si>
+  <si>
+    <t>Inject Dana</t>
+  </si>
+  <si>
+    <t>Pemeliharaan Rumput</t>
+  </si>
+  <si>
+    <t>Obat Rumput</t>
+  </si>
+  <si>
+    <t>Listrik Juli</t>
+  </si>
+  <si>
+    <t>Jasa Pemeliharaan Rumput</t>
+  </si>
+  <si>
+    <t>Bensin Mesin Pemotong Rumput</t>
+  </si>
+  <si>
+    <t>Makan Siang Jasa Pemeliharaan Rumput</t>
+  </si>
+  <si>
+    <t>Jamuan Air Jasa Pemeliharaan Rumput</t>
+  </si>
+  <si>
+    <t>Lem Pipa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -250,12 +272,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -267,6 +288,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -684,21 +709,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="30.08984375" style="10" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="47.1796875" customWidth="1"/>
-    <col min="4" max="4" width="20.1796875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="12" style="4" customWidth="1"/>
-    <col min="6" max="6" width="20.90625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20.90625" style="3" customWidth="1"/>
     <col min="8" max="8" width="19.54296875" customWidth="1"/>
     <col min="9" max="9" width="12.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -707,18 +732,18 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
+      <c r="A2" s="10">
         <v>46122</v>
       </c>
       <c r="B2" t="s">
@@ -727,19 +752,19 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>2500000</v>
       </c>
-      <c r="E2" s="4">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4">
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
         <f>D2-E2</f>
         <v>2500000</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
+      <c r="A3" s="10">
         <v>46122</v>
       </c>
       <c r="B3" t="s">
@@ -748,19 +773,19 @@
       <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>2500000</v>
       </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4">
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
         <f>D3-E3</f>
         <v>2500000</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
+      <c r="A4" s="10">
         <v>46123</v>
       </c>
       <c r="B4" t="s">
@@ -769,19 +794,19 @@
       <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
         <v>50000</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <f>F3-E4</f>
         <v>2450000</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
+      <c r="A5" s="10">
         <v>46123</v>
       </c>
       <c r="B5" t="s">
@@ -790,19 +815,19 @@
       <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
         <v>50000</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <f>F2-E5</f>
         <v>2450000</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
+      <c r="A6" s="10">
         <v>46132</v>
       </c>
       <c r="B6" t="s">
@@ -811,19 +836,19 @@
       <c r="C6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
         <v>69200</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <f>F4-E6</f>
         <v>2380800</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
+      <c r="A7" s="10">
         <v>46133</v>
       </c>
       <c r="B7" t="s">
@@ -832,19 +857,19 @@
       <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
         <v>9000</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <f>F6-E7</f>
         <v>2371800</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+      <c r="A8" s="10">
         <v>46133</v>
       </c>
       <c r="B8" t="s">
@@ -853,19 +878,19 @@
       <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
         <v>9000</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="3">
         <f>F5-E8</f>
         <v>2441000</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
+      <c r="A9" s="10">
         <v>46133</v>
       </c>
       <c r="B9" t="s">
@@ -874,20 +899,20 @@
       <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
         <f>67800/2</f>
         <v>33900</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="3">
         <f>F7-E9</f>
         <v>2337900</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
+      <c r="A10" s="10">
         <v>46133</v>
       </c>
       <c r="B10" t="s">
@@ -896,583 +921,961 @@
       <c r="C10" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
         <v>33900</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="3">
         <f>F8-E10</f>
         <v>2407100</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
+      <c r="A11" s="10">
         <v>46134</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4">
+        <v>42</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
         <v>250000</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <f>F10-E11</f>
         <v>2157100</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
+      <c r="A12" s="10">
         <v>46134</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
+        <v>42</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
         <v>250000</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <f>F9-E12</f>
         <v>2087900</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
+      <c r="A13" s="10">
         <v>46135</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="4">
+        <v>33</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
         <v>200000</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="3">
         <f>F11-E13</f>
         <v>1957100</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
+      <c r="A14" s="10">
         <v>46134</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4">
+        <v>43</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>25000</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="3">
         <f>F12-E14</f>
         <v>2062900</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
+      <c r="A15" s="10">
         <v>46134</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="E15" s="4">
+        <v>43</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>25000</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="3">
         <f>F13-E15</f>
         <v>1932100</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
+      <c r="A16" s="10">
         <v>46143</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4">
+        <v>26</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
         <v>200000</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="3">
         <f>F15-E16</f>
         <v>1732100</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
+      <c r="A17" s="10">
         <v>46143</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="4">
+        <v>27</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
         <v>500000</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="3">
         <f>F16-E17</f>
         <v>1232100</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
+      <c r="A18" s="10">
         <v>46143</v>
       </c>
       <c r="B18" t="s">
         <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4">
+        <v>26</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
         <v>185000</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="3">
         <f>F14-E18</f>
         <v>1877900</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
+      <c r="A19" s="10">
         <v>46143</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0</v>
-      </c>
-      <c r="E19" s="4">
+        <v>28</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3">
         <v>31000</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="3">
         <f>F17-E19</f>
         <v>1201100</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
+      <c r="A20" s="10">
         <v>46162</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="4">
+        <v>29</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>99345</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="3">
         <f>F19-E20</f>
         <v>1101755</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
+      <c r="A21" s="10">
         <v>46162</v>
       </c>
       <c r="B21" t="s">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="4">
+        <v>29</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>99345</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="3">
         <f>F18-E21</f>
         <v>1778555</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
+      <c r="A22" s="10">
         <v>46174</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4">
+        <v>32</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
         <v>250000</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="3">
         <f>F20-E22</f>
         <v>851755</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="2">
+      <c r="A23" s="10">
         <v>46174</v>
       </c>
       <c r="B23" t="s">
         <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0</v>
-      </c>
-      <c r="E23" s="4">
+        <v>32</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
         <v>250000</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="3">
         <f>F21-E23</f>
         <v>1528555</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
+      <c r="A24" s="10">
         <v>46174</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="4">
-        <v>0</v>
-      </c>
-      <c r="E24" s="4">
+        <v>26</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>245000</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="3">
         <f>F22-E24</f>
         <v>606755</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="2">
+      <c r="A25" s="10">
         <v>46174</v>
       </c>
       <c r="B25" t="s">
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0</v>
-      </c>
-      <c r="E25" s="4">
+        <v>26</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
         <v>200000</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="3">
         <f>F23-E25</f>
         <v>1328555</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
+      <c r="A26" s="10">
         <v>46174</v>
       </c>
       <c r="B26" t="s">
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0</v>
-      </c>
-      <c r="E26" s="4">
+        <v>29</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
         <v>155000</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="3">
         <f>F25-E26</f>
         <v>1173555</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="2">
+      <c r="A27" s="10">
         <v>46174</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0</v>
-      </c>
-      <c r="E27" s="4">
+        <v>29</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>155000</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="3">
         <f>F24-E27</f>
         <v>451755</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="2">
+      <c r="A28" s="10">
         <v>46174</v>
       </c>
       <c r="B28" t="s">
         <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0</v>
-      </c>
-      <c r="E28" s="4">
+        <v>28</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3">
         <v>46500</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="3">
         <f>F26-E28</f>
         <v>1127055</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="2">
+      <c r="A29" s="10">
         <v>46174</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0</v>
-      </c>
-      <c r="E29" s="4">
+        <v>28</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <f>46500</f>
         <v>46500</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="3">
         <f>F27-E29</f>
         <v>405255</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="2">
+      <c r="A30" s="10">
         <v>46201</v>
       </c>
       <c r="B30" t="s">
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="4">
-        <v>0</v>
-      </c>
-      <c r="E30" s="4">
+        <v>34</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3">
         <v>250000</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="3">
         <f>F28-E30</f>
         <v>877055</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="2">
+      <c r="A31" s="10">
         <v>46201</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="4">
-        <v>0</v>
-      </c>
-      <c r="E31" s="4">
+        <v>34</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3">
         <v>250000</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="3">
         <f>F29-E31</f>
         <v>155255</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="2">
+      <c r="A32" s="10">
         <v>46201</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0</v>
-      </c>
-      <c r="E32" s="4">
+        <v>36</v>
+      </c>
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>50000</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="3">
         <f>F31-E32</f>
         <v>105255</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="2">
+      <c r="A33" s="10">
         <v>46201</v>
       </c>
       <c r="B33" t="s">
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0</v>
-      </c>
-      <c r="E33" s="4">
+        <v>37</v>
+      </c>
+      <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
         <v>5000</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="3">
         <f>F32-E33</f>
         <v>100255</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="2">
+      <c r="A34" s="10">
         <v>46201</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0</v>
-      </c>
-      <c r="E34" s="4">
+        <v>38</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3">
         <v>22500</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="3">
         <f>F33-E34</f>
         <v>77755</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="2">
+      <c r="A35" s="10">
         <v>46201</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" s="4">
-        <v>0</v>
-      </c>
-      <c r="E35" s="4">
+        <v>39</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
         <v>22500</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="3">
         <f>F30-E35</f>
         <v>854555</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="2">
+      <c r="A36" s="10">
         <v>46201</v>
       </c>
       <c r="B36" t="s">
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="4">
-        <v>0</v>
-      </c>
-      <c r="E36" s="4">
+        <v>35</v>
+      </c>
+      <c r="D36" s="3">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3">
         <v>168000</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="3">
         <f>F35-E36</f>
         <v>686555</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="2">
+      <c r="A37" s="10">
         <v>46201</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>42</v>
-      </c>
-      <c r="D37" s="4">
-        <v>0</v>
-      </c>
-      <c r="E37" s="4">
+        <v>40</v>
+      </c>
+      <c r="D37" s="3">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3">
         <v>85280</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F37" s="3">
         <f>F36-E37</f>
         <v>601275</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="10">
+        <v>46204</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3">
+        <f>F34+D38</f>
+        <v>1077755</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="10">
+        <v>46204</v>
+      </c>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="3">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3">
+        <v>245000</v>
+      </c>
+      <c r="F39" s="3">
+        <f>F38-E39</f>
+        <v>832755</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="10">
+        <v>46204</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" s="3">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3">
+        <v>200000</v>
+      </c>
+      <c r="F40" s="3">
+        <f>F37-E40</f>
+        <v>401275</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="10">
+        <v>46208</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
+        <f>F40+D41</f>
+        <v>1401275</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="10">
+        <v>46208</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>150000</v>
+      </c>
+      <c r="F42" s="3">
+        <f>F41-E42</f>
+        <v>1251275</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="10">
+        <v>46208</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>150000</v>
+      </c>
+      <c r="F43" s="3">
+        <f>F39-E43</f>
+        <v>682755</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="10">
+        <v>46208</v>
+      </c>
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F44" s="3">
+        <f>F43-E44</f>
+        <v>671755</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="10">
+        <v>46208</v>
+      </c>
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F45" s="3">
+        <f>F44-E45</f>
+        <v>661755</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="10">
+        <v>46208</v>
+      </c>
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" s="3">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F46" s="3">
+        <f>F45-E46</f>
+        <v>654755</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="10">
+        <v>46208</v>
+      </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F47" s="3">
+        <f>F42-E47</f>
+        <v>1240275</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="10">
+        <v>46208</v>
+      </c>
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" t="s">
+        <v>46</v>
+      </c>
+      <c r="D48" s="3">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F48" s="3">
+        <f>F47-E48</f>
+        <v>1230275</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="10">
+        <v>46208</v>
+      </c>
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" t="s">
+        <v>48</v>
+      </c>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F49" s="3">
+        <f>F48-E49</f>
+        <v>1223275</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="10">
+        <v>46208</v>
+      </c>
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D50" s="3">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F50" s="3">
+        <f>F49-E50</f>
+        <v>1216275</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="10">
+        <v>46208</v>
+      </c>
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D51" s="3">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3">
+        <v>5250</v>
+      </c>
+      <c r="F51" s="3">
+        <f>F50-E51</f>
+        <v>1211025</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B52" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>250000</v>
+      </c>
+      <c r="F52" s="3">
+        <f>F46-E52</f>
+        <v>404755</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D53" s="3">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3">
+        <v>250000</v>
+      </c>
+      <c r="F53" s="3">
+        <f>F51-E53</f>
+        <v>961025</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" t="s">
+        <v>28</v>
+      </c>
+      <c r="D54" s="3">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3">
+        <v>105500</v>
+      </c>
+      <c r="F54" s="3">
+        <f>F53-E54</f>
+        <v>855525</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" s="3">
+        <v>0</v>
+      </c>
+      <c r="E55" s="3">
+        <v>105500</v>
+      </c>
+      <c r="F55" s="3">
+        <f>F52-E55</f>
+        <v>299255</v>
       </c>
     </row>
   </sheetData>
@@ -1518,37 +1921,37 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="4">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3">
         <f>SUMIF('Master Kas'!B:B,"Kas Rayhan",'Master Kas'!D:D)</f>
-        <v>2500000</v>
-      </c>
-      <c r="C2" s="4">
+        <v>3500000</v>
+      </c>
+      <c r="C2" s="3">
         <f>SUMIF('Master Kas'!B:B,"Kas Rayhan",'Master Kas'!E:E)</f>
-        <v>1898725</v>
-      </c>
-      <c r="D2" s="4">
+        <v>2639225</v>
+      </c>
+      <c r="D2" s="3">
         <f>B2-C2</f>
-        <v>601275</v>
+        <v>860775</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="4">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3">
         <f>SUMIF('Master Kas'!B:B,"Kas Azka",'Master Kas'!D:D)</f>
-        <v>2500000</v>
-      </c>
-      <c r="C3" s="4">
+        <v>3500000</v>
+      </c>
+      <c r="C3" s="3">
         <f>SUMIF('Master Kas'!B:B,"Kas Azka",'Master Kas'!E:E)</f>
-        <v>2422245</v>
-      </c>
-      <c r="D3" s="4">
+        <v>3205995</v>
+      </c>
+      <c r="D3" s="3">
         <f>B3-C3</f>
-        <v>77755</v>
+        <v>294005</v>
       </c>
     </row>
   </sheetData>
@@ -1566,39 +1969,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="3"/>
+      <c r="B1" s="2"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <f>'Sisa Kas'!D2</f>
-        <v>601275</v>
+        <v>860775</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>715000</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <f>IFERROR(B3/B4,0)</f>
-        <v>0.84094405594405597</v>
+        <v>1.2038811188811189</v>
       </c>
     </row>
   </sheetData>
@@ -1617,113 +2020,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="10"/>
+      <c r="A1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="11"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="8">
         <v>200000</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="9">
-        <v>165000</v>
+      <c r="B4" s="8">
+        <v>155000</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <v>300000</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>50000</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <f>SUM(B3:B6)</f>
-        <v>715000</v>
+        <v>705000</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="10"/>
+      <c r="A9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="11"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="8">
         <v>245000</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="9">
-        <v>165000</v>
+      <c r="B12" s="8">
+        <v>155000</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="8">
         <v>300000</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="8">
         <v>50000</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="8">
         <f>SUM(B11:B14)</f>
-        <v>760000</v>
+        <v>750000</v>
       </c>
     </row>
   </sheetData>
